--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487010_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487010_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4254</v>
+        <v>1.6932</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0306</v>
+        <v>1.6525</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3949</v>
+        <v>0.0406</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4798</v>
+        <v>0.6331</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2727</v>
+        <v>0.2725</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.3606</v>
       </c>
       <c r="J2" t="n">
-        <v>0.624</v>
+        <v>1.6217</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0584</v>
+        <v>0.9378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5656</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1441</v>
+        <v>-0.9887</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3311</v>
+        <v>-0.6653</v>
       </c>
       <c r="O2" t="n">
-        <v>0.187</v>
+        <v>-0.3234</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9456</v>
+        <v>0.0416</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4333</v>
+        <v>0.0308</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4877</v>
+        <v>0.0108</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4024</v>
+        <v>0.7887</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2729</v>
+        <v>0.3642</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1296</v>
+        <v>0.4245</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6331</v>
+        <v>0.4798</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2725</v>
+        <v>-0.2727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3606</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6217</v>
+        <v>0.624</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9378</v>
+        <v>0.0584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5656</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9887</v>
+        <v>-0.1441</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6653</v>
+        <v>-0.3311</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3234</v>
+        <v>0.187</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2492</v>
+        <v>0.3089</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3489</v>
+        <v>0.767</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0997</v>
+        <v>-0.4581</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3822</v>
+        <v>-0.0255</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1957</v>
+        <v>1.6412</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5778</v>
+        <v>-1.6668</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4429</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.315</v>
+        <v>0.0416</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4806</v>
+        <v>-0.0351</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1656</v>
+        <v>0.0766</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2801</v>
+        <v>-0.791</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9683</v>
+        <v>-1.6274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6882</v>
+        <v>0.8364</v>
       </c>
       <c r="G5" t="n">
         <v>-2.7659</v>
@@ -844,13 +844,13 @@
         <v>2.2588</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0134</v>
+        <v>0.5026</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2903</v>
+        <v>0.6313</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2769</v>
+        <v>-0.1287</v>
       </c>
       <c r="V5" t="n">
         <v>0.2402</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8723</v>
+        <v>-2.0815</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0937</v>
+        <v>0.8845</v>
       </c>
       <c r="F6" t="n">
         <v>-2.966</v>
@@ -922,10 +922,10 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0968</v>
+        <v>-0.1124</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.1319</v>
       </c>
       <c r="U6" t="n">
         <v>0.0195</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2062</v>
+        <v>-2.5431</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4984</v>
+        <v>-1.7464</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7078</v>
+        <v>-0.7967</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6242</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.301</v>
+        <v>-0.0359</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5384</v>
+        <v>0.2904</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2374</v>
+        <v>-0.3263</v>
       </c>
       <c r="V7" t="n">
         <v>0.9384</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0111</v>
+        <v>-2.8769</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4986</v>
+        <v>-1.394</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5126</v>
+        <v>-1.4829</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3912</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4413</v>
+        <v>-0.3071</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0464</v>
+        <v>0.151</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4877</v>
+        <v>-0.4581</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9543</v>
+        <v>-3.1283</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7902</v>
+        <v>-4.2013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8359</v>
+        <v>1.073</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7593</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0431</v>
+        <v>-0.217</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1513</v>
+        <v>0.4376</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8918</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.764</v>
+        <v>-5.3558</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7096</v>
+        <v>-2.7872</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0544</v>
+        <v>-2.5686</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.9955</v>
+        <v>-3.1409</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.0802</v>
+        <v>-0.8986</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9154</v>
+        <v>-2.2422</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5784</v>
+        <v>-0.8104</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7757</v>
+        <v>0.2954</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1973</v>
+        <v>-1.1058</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4171</v>
+        <v>-2.3305</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3044</v>
+        <v>-1.194</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1127</v>
+        <v>-1.1365</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>1.285</v>
+        <v>0.1772</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1194</v>
+        <v>-0.252</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1656</v>
+        <v>0.4292</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5893</v>
+        <v>-2.5975</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8295</v>
+        <v>-0.6982</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2402</v>
+        <v>-1.8993</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8558</v>
+        <v>-5.5192</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3761</v>
+        <v>-4.3759</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4797</v>
+        <v>-1.1433</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1409</v>
+        <v>-4.9955</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8986</v>
+        <v>-4.0802</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2422</v>
+        <v>-0.9154</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8104</v>
+        <v>-2.5784</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2954</v>
+        <v>-2.7757</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1058</v>
+        <v>0.1973</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3305</v>
+        <v>-2.4171</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.194</v>
+        <v>-1.3044</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1365</v>
+        <v>-1.1127</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2053</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3228</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8409</v>
+        <v>0.4531</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5181</v>
+        <v>0.0766</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5975</v>
+        <v>0.5893</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6982</v>
+        <v>0.8295</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8993</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.4982</v>
+        <v>-19.8394</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.2483</v>
+        <v>-11.5898</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.249700000000001</v>
+        <v>-8.2498</v>
       </c>
       <c r="G12" t="n">
         <v>-21.2081</v>
@@ -1366,7 +1366,7 @@
         <v>-8.4017</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.1757</v>
+        <v>-6.175700000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-2.226</v>
@@ -1375,7 +1375,7 @@
         <v>-12.8063</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.572399999999998</v>
+        <v>-9.5724</v>
       </c>
       <c r="O12" t="n">
         <v>-3.234</v>
@@ -1390,16 +1390,16 @@
         <v>14.3741</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2704</v>
+        <v>0.9292</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6834</v>
+        <v>2.3422</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.413</v>
+        <v>-1.4132</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.6672</v>
+        <v>-3.667200000000001</v>
       </c>
       <c r="W12" t="n">
         <v>4.7369</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.654</v>
+        <v>8.6965</v>
       </c>
       <c r="E13" t="n">
-        <v>5.954</v>
+        <v>6.157</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.5395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5878</v>
+        <v>6.6193</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7774</v>
+        <v>0.947</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8104</v>
+        <v>5.6724</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8423</v>
+        <v>5.5949</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3821</v>
+        <v>0.4122</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4602</v>
+        <v>5.1827</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7455000000000001</v>
+        <v>1.0245</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3953</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3502</v>
+        <v>0.4897</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>2.485</v>
+        <v>-0.6005</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9331</v>
+        <v>-0.2674</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.333</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9384</v>
+        <v>0.8295</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1786</v>
+        <v>0.8295</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6783</v>
+        <v>7.0117</v>
       </c>
       <c r="E14" t="n">
-        <v>5.634</v>
+        <v>4.4896</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0443</v>
+        <v>2.5221</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6193</v>
+        <v>3.5878</v>
       </c>
       <c r="H14" t="n">
-        <v>0.947</v>
+        <v>1.7774</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6724</v>
+        <v>1.8104</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5949</v>
+        <v>2.8423</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4122</v>
+        <v>1.3821</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1827</v>
+        <v>1.4602</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0245</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.3953</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4897</v>
+        <v>0.3502</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6187</v>
+        <v>0.8427</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7905</v>
+        <v>0.4686</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8282</v>
+        <v>0.3741</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8295</v>
+        <v>0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8295</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4099</v>
+        <v>4.7736</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9007</v>
+        <v>4.273</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5093</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.6361</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1023</v>
+        <v>0.466</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2125</v>
+        <v>0.5849</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1102</v>
+        <v>-0.1189</v>
       </c>
       <c r="V15" t="n">
         <v>2.4661</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9922</v>
+        <v>3.2537</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0503</v>
+        <v>0.7365</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9419</v>
+        <v>2.5173</v>
       </c>
       <c r="G16" t="n">
         <v>3.0688</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2285</v>
+        <v>0.033</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0149</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2434</v>
+        <v>-0.6681</v>
       </c>
       <c r="V16" t="n">
         <v>1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5513</v>
+        <v>0.7448</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1317</v>
+        <v>-0.0271</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.772</v>
       </c>
       <c r="G17" t="n">
         <v>0.6974</v>
@@ -1780,13 +1780,13 @@
         <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3514</v>
+        <v>-0.1579</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1317</v>
+        <v>-0.0271</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1905</v>
+        <v>0.6155</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2758</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0853</v>
+        <v>1.4729</v>
       </c>
       <c r="G18" t="n">
         <v>1.0282</v>
@@ -1858,13 +1858,13 @@
         <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5493</v>
+        <v>0.2568</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6433</v>
+        <v>-0.2249</v>
       </c>
       <c r="U18" t="n">
-        <v>0.094</v>
+        <v>0.4816</v>
       </c>
       <c r="V18" t="n">
         <v>1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3986</v>
+        <v>-0.2644</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7632</v>
+        <v>-0.6586</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3646</v>
+        <v>0.3942</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5579</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0461</v>
+        <v>0.0881</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.907</v>
+        <v>-0.3346</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1429</v>
+        <v>-1.8869</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0499</v>
+        <v>1.5523</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0434</v>
+        <v>3.9751</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1778</v>
+        <v>4.6066</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8656</v>
+        <v>-0.6315</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3246</v>
+        <v>3.0135</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7855</v>
+        <v>3.7637</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5391</v>
+        <v>-0.7502</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7188</v>
+        <v>0.9616</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3923</v>
+        <v>0.8428</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3264</v>
+        <v>0.1188</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-5.1336</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-6.1603</v>
       </c>
       <c r="R21" t="n">
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5931</v>
+        <v>-0.0057</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3952</v>
+        <v>-0.159</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1979</v>
+        <v>0.1533</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3573</v>
+        <v>0.8295</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5975</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0912</v>
+        <v>-0.4136</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3053</v>
+        <v>0.6659</v>
       </c>
       <c r="F22" t="n">
-        <v>1.214</v>
+        <v>-1.0795</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9751</v>
+        <v>2.0434</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6066</v>
+        <v>1.1778</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6315</v>
+        <v>0.8656</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0135</v>
+        <v>1.3246</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7637</v>
+        <v>0.7855</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7502</v>
+        <v>0.5391</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9616</v>
+        <v>0.7188</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8428</v>
+        <v>0.3923</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1188</v>
+        <v>0.3264</v>
       </c>
       <c r="P22" t="n">
-        <v>-5.1336</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.1603</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7623</v>
+        <v>-0.0997</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5774</v>
+        <v>0.1278</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1849</v>
+        <v>-0.2275</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8295</v>
+        <v>-2.3573</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4189</v>
+        <v>0.2402</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5893</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9974</v>
+        <v>-1.9383</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.561</v>
+        <v>-3.2472</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5635</v>
+        <v>1.3089</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8117</v>
@@ -2248,13 +2248,13 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1017</v>
+        <v>0.1609</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1163</v>
+        <v>0.1975</v>
       </c>
       <c r="U23" t="n">
-        <v>0.218</v>
+        <v>-0.0366</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6982</v>
@@ -2281,37 +2281,37 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>20.4984</v>
+        <v>21.9423</v>
       </c>
       <c r="E24" t="n">
-        <v>8.2499</v>
+        <v>8.249799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>12.2483</v>
+        <v>13.6925</v>
       </c>
       <c r="G24" t="n">
-        <v>21.20820000000001</v>
+        <v>21.2082</v>
       </c>
       <c r="H24" t="n">
         <v>15.7482</v>
       </c>
       <c r="I24" t="n">
-        <v>5.459999999999999</v>
+        <v>5.460000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>12.8063</v>
       </c>
       <c r="K24" t="n">
-        <v>9.572499999999998</v>
+        <v>9.5725</v>
       </c>
       <c r="L24" t="n">
-        <v>3.2341</v>
+        <v>3.234099999999999</v>
       </c>
       <c r="M24" t="n">
         <v>8.4018</v>
       </c>
       <c r="N24" t="n">
-        <v>6.175699999999999</v>
+        <v>6.1757</v>
       </c>
       <c r="O24" t="n">
         <v>2.226</v>
@@ -2326,16 +2326,16 @@
         <v>10.267</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2705</v>
+        <v>1.1736</v>
       </c>
       <c r="T24" t="n">
         <v>1.413</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6835</v>
+        <v>-0.2393000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>3.667000000000001</v>
+        <v>3.667000000000002</v>
       </c>
       <c r="W24" t="n">
         <v>8.404200000000001</v>
